--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.78789563512849</v>
+        <v>3.54053304070838</v>
       </c>
       <c r="D2" t="n">
-        <v>25.03897718366229</v>
+        <v>4.068833792345122</v>
       </c>
       <c r="E2" t="n">
-        <v>3.933599250407101</v>
+        <v>0.6392098781911542</v>
       </c>
       <c r="F2" t="n">
-        <v>7.281892774797597</v>
+        <v>1.183307575904609</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.81114729337145</v>
+        <v>2.56931143517286</v>
       </c>
       <c r="D3" t="n">
-        <v>18.64783077790685</v>
+        <v>3.030272501409864</v>
       </c>
       <c r="E3" t="n">
-        <v>3.933599250407101</v>
+        <v>0.6392098781911542</v>
       </c>
       <c r="F3" t="n">
-        <v>7.281892774797597</v>
+        <v>1.183307575904609</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.95696511944051</v>
+        <v>2.593006831909082</v>
       </c>
       <c r="D4" t="n">
-        <v>12.92692338009805</v>
+        <v>2.100625049265934</v>
       </c>
       <c r="E4" t="n">
-        <v>3.933599250407101</v>
+        <v>0.6392098781911542</v>
       </c>
       <c r="F4" t="n">
-        <v>7.281892774797597</v>
+        <v>1.183307575904609</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.03023838342279</v>
+        <v>4.067413737306205</v>
       </c>
       <c r="D5" t="n">
-        <v>5.273300023759194</v>
+        <v>0.856911253860869</v>
       </c>
       <c r="E5" t="n">
-        <v>3.933599250407101</v>
+        <v>0.6392098781911542</v>
       </c>
       <c r="F5" t="n">
-        <v>7.281892774797597</v>
+        <v>1.183307575904609</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
